--- a/diseases/d064/2010-2014.xlsx
+++ b/diseases/d064/2010-2014.xlsx
@@ -905,9 +905,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1293,9 +1290,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1581,9 +1575,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1869,9 +1860,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2157,9 +2145,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2445,9 +2430,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2733,9 +2715,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3021,9 +3000,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3309,9 +3285,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3597,9 +3570,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3885,9 +3855,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4173,9 +4140,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4461,9 +4425,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4749,9 +4710,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5137,9 +5095,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5425,9 +5380,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5713,9 +5665,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6001,9 +5950,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6289,9 +6235,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6577,9 +6520,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -6865,9 +6805,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7153,9 +7090,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7441,9 +7375,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -7729,9 +7660,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8017,9 +7945,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8305,9 +8230,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8593,9 +8515,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -8981,9 +8900,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9269,9 +9185,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9557,9 +9470,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -9845,9 +9755,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10133,9 +10040,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10421,9 +10325,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10709,9 +10610,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -10997,9 +10895,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11285,9 +11180,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -12005,9 +11897,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -12869,9 +12758,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -13877,9 +13763,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14741,9 +14624,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15129,9 +15009,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -16137,9 +16014,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -17001,9 +16875,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -17865,9 +17736,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -18729,9 +18597,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -19737,9 +19602,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -20601,9 +20463,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -21465,9 +21324,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -22473,9 +22329,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -23337,9 +23190,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -24345,9 +24195,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -25209,9 +25056,6 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -26073,9 +25917,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
@@ -26461,9 +26302,6 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -27469,9 +27307,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -28333,9 +28168,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -29197,9 +29029,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -30061,9 +29890,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -31069,9 +30895,6 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
@@ -31933,9 +31756,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -32941,9 +32761,6 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -33805,9 +33622,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -34669,9 +34483,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -35677,9 +35488,6 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -36539,9 +36347,6 @@
         <v>0</v>
       </c>
       <c r="O247" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q247" t="n">
         <v>0</v>
       </c>
       <c r="R247" t="n">
